--- a/inventories/optimized/lci-Salar-de-Cauchari-Olaroz.xlsx
+++ b/inventories/optimized/lci-Salar-de-Cauchari-Olaroz.xlsx
@@ -822,7 +822,7 @@
         <v>27</v>
       </c>
       <c r="B26">
-        <v>-0.00822873443403753</v>
+        <v>-0.008228734434037531</v>
       </c>
       <c r="D26" t="s">
         <v>28</v>
@@ -890,7 +890,7 @@
         <v>30</v>
       </c>
       <c r="B30">
-        <v>0.02953261935758535</v>
+        <v>0.02953261935758534</v>
       </c>
       <c r="C30" t="s">
         <v>31</v>
@@ -941,7 +941,7 @@
         <v>35</v>
       </c>
       <c r="B33">
-        <v>0.0003707875609385734</v>
+        <v>0.0003707875609385735</v>
       </c>
       <c r="C33" t="s">
         <v>31</v>
@@ -1222,7 +1222,7 @@
         <v>3</v>
       </c>
       <c r="B60">
-        <v>0.5411967065565291</v>
+        <v>0.5201844889210736</v>
       </c>
       <c r="C60" t="s">
         <v>1</v>
@@ -1239,7 +1239,7 @@
         <v>41</v>
       </c>
       <c r="B61">
-        <v>0.3235041168043387</v>
+        <v>0.3497693888486581</v>
       </c>
       <c r="C61" t="s">
         <v>1</v>
@@ -1256,7 +1256,7 @@
         <v>39</v>
       </c>
       <c r="B62">
-        <v>0.08282616421814579</v>
+        <v>0.08955081352730072</v>
       </c>
       <c r="C62" t="s">
         <v>1</v>
@@ -1273,7 +1273,7 @@
         <v>42</v>
       </c>
       <c r="B63">
-        <v>0.1352991766391323</v>
+        <v>0.1300461222302684</v>
       </c>
       <c r="C63" t="s">
         <v>33</v>
@@ -1388,7 +1388,7 @@
         <v>3</v>
       </c>
       <c r="B75">
-        <v>0.0004885719404391603</v>
+        <v>0.0004885719404391602</v>
       </c>
       <c r="C75" t="s">
         <v>1</v>
@@ -1554,7 +1554,7 @@
         <v>3</v>
       </c>
       <c r="B90">
-        <v>0.0009290216355945331</v>
+        <v>0.000929021635594533</v>
       </c>
       <c r="C90" t="s">
         <v>1</v>
@@ -1588,7 +1588,7 @@
         <v>42</v>
       </c>
       <c r="B92">
-        <v>0.0002322554088986333</v>
+        <v>0.0002322554088986332</v>
       </c>
       <c r="C92" t="s">
         <v>33</v>
@@ -1852,7 +1852,7 @@
         <v>40</v>
       </c>
       <c r="B118">
-        <v>7.067997269553163</v>
+        <v>7.353500393997901</v>
       </c>
       <c r="C118" t="s">
         <v>1</v>
@@ -1869,7 +1869,7 @@
         <v>22</v>
       </c>
       <c r="B119">
-        <v>0.00677832525030918</v>
+        <v>0.007052127427030774</v>
       </c>
       <c r="C119" t="s">
         <v>23</v>
@@ -2018,7 +2018,7 @@
         <v>22</v>
       </c>
       <c r="B133">
-        <v>3.187993818510206E-05</v>
+        <v>3.187993818510205E-05</v>
       </c>
       <c r="C133" t="s">
         <v>23</v>
@@ -2184,7 +2184,7 @@
         <v>36</v>
       </c>
       <c r="B148">
-        <v>-0.0004410870613624542</v>
+        <v>-0.0004410870613624541</v>
       </c>
       <c r="C148" t="s">
         <v>31</v>
@@ -2580,7 +2580,7 @@
         <v>54</v>
       </c>
       <c r="B187">
-        <v>0.0547945205426546</v>
+        <v>0.0482329255631993</v>
       </c>
       <c r="D187" t="s">
         <v>11</v>
@@ -2597,7 +2597,7 @@
         <v>55</v>
       </c>
       <c r="B188">
-        <v>5.813864227913049E-11</v>
+        <v>5.117659170339588E-11</v>
       </c>
       <c r="D188" t="s">
         <v>56</v>
@@ -2614,7 +2614,7 @@
         <v>58</v>
       </c>
       <c r="B189">
-        <v>1.453466056978262E-12</v>
+        <v>1.279414792584897E-12</v>
       </c>
       <c r="D189" t="s">
         <v>59</v>
@@ -2631,7 +2631,7 @@
         <v>60</v>
       </c>
       <c r="B190">
-        <v>1.453466056978262E-12</v>
+        <v>1.279414792584897E-12</v>
       </c>
       <c r="D190" t="s">
         <v>59</v>
@@ -2682,7 +2682,7 @@
         <v>3</v>
       </c>
       <c r="B193">
-        <v>0.2961105619218378</v>
+        <v>0.3804006945344577</v>
       </c>
       <c r="C193" t="s">
         <v>1</v>
@@ -2699,7 +2699,7 @@
         <v>61</v>
       </c>
       <c r="B194">
-        <v>0.0002408447063434366</v>
+        <v>0.0002120037674991724</v>
       </c>
       <c r="C194" t="s">
         <v>1</v>
@@ -2716,7 +2716,7 @@
         <v>22</v>
       </c>
       <c r="B195">
-        <v>0.00338744236901186</v>
+        <v>0.002982169215047077</v>
       </c>
       <c r="C195" t="s">
         <v>23</v>
@@ -2733,7 +2733,7 @@
         <v>45</v>
       </c>
       <c r="B196">
-        <v>3.005572901530621E-10</v>
+        <v>0.3727677076868997</v>
       </c>
       <c r="C196" t="s">
         <v>31</v>
@@ -2750,7 +2750,7 @@
         <v>63</v>
       </c>
       <c r="B197">
-        <v>0.0005329990112855144</v>
+        <v>0.0004691728549131233</v>
       </c>
       <c r="C197" t="s">
         <v>31</v>
@@ -2767,7 +2767,7 @@
         <v>64</v>
       </c>
       <c r="B198">
-        <v>-31.55252682824166</v>
+        <v>-27.77413987321477</v>
       </c>
       <c r="C198" t="s">
         <v>31</v>
@@ -2784,7 +2784,7 @@
         <v>48</v>
       </c>
       <c r="B199">
-        <v>-0.0002961105618252858</v>
+        <v>-0.0002606515860628463</v>
       </c>
       <c r="C199" t="s">
         <v>1</v>
@@ -2950,7 +2950,7 @@
         <v>3</v>
       </c>
       <c r="B214">
-        <v>0.1760784356239004</v>
+        <v>0.1726244874790738</v>
       </c>
       <c r="C214" t="s">
         <v>1</v>
@@ -3333,7 +3333,7 @@
         <v>71</v>
       </c>
       <c r="B247">
-        <v>0.006562086665157991</v>
+        <v>0.006562086665157992</v>
       </c>
       <c r="C247" t="s">
         <v>31</v>
@@ -3465,7 +3465,7 @@
         <v>65</v>
       </c>
       <c r="B260">
-        <v>2.84836634361465</v>
+        <v>2.876667312052341</v>
       </c>
       <c r="C260" t="s">
         <v>1</v>
@@ -3482,7 +3482,7 @@
         <v>39</v>
       </c>
       <c r="B261">
-        <v>0.3022047218225299</v>
+        <v>0.3052073855470167</v>
       </c>
       <c r="C261" t="s">
         <v>1</v>
@@ -3499,7 +3499,7 @@
         <v>22</v>
       </c>
       <c r="B262">
-        <v>0.003751506891590027</v>
+        <v>0.003788781337825035</v>
       </c>
       <c r="C262" t="s">
         <v>23</v>
@@ -3516,7 +3516,7 @@
         <v>72</v>
       </c>
       <c r="B263">
-        <v>0.02310457929518313</v>
+        <v>0.02345834140065427</v>
       </c>
       <c r="C263" t="s">
         <v>31</v>
